--- a/templates/filled-examples/FILLED_INVENTORY.xlsx
+++ b/templates/filled-examples/FILLED_INVENTORY.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="128">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -308,6 +308,9 @@
     <t>An IMEI already in the system UPDATES that unit; a new IMEI CREATES one. Re-uploading the same file is safe.</t>
   </si>
   <si>
+    <t>SHS rows leave IMEI BLANK — supplier-held stock has not shipped, so there is no IMEI yet. It is captured when you Receive the unit.</t>
+  </si>
+  <si>
     <t>Column</t>
   </si>
   <si>
@@ -338,10 +341,13 @@
     <t>Brand and storage are parsed out of this string where possible. Keep it consistent — it is how stock groups together across the app.</t>
   </si>
   <si>
+    <t>Office only</t>
+  </si>
+  <si>
     <t>15 digits, or a 10-12 character Apple serial</t>
   </si>
   <si>
-    <t>The unique key for the unit. An existing IMEI updates that unit rather than creating a duplicate. Invalid IMEIs are listed in the preview and skipped.</t>
+    <t>The unique key for the unit. An existing IMEI updates that unit rather than creating a duplicate. REQUIRED for OFFICE stock; leave BLANK for SHS — supplier-held stock has not shipped, so there is no IMEI to record yet. It is captured on Receive. Invalid IMEIs are listed in the preview and skipped.</t>
   </si>
   <si>
     <t>A, B, C, ONU, Brand new</t>
@@ -2197,7 +2203,7 @@
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2231,68 +2237,59 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="7" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>110</v>
@@ -2303,10 +2300,10 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>112</v>
@@ -2317,10 +2314,10 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>114</v>
@@ -2331,10 +2328,10 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>116</v>
@@ -2345,10 +2342,10 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>105</v>
+        <v>6</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>118</v>
@@ -2359,10 +2356,10 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>120</v>
@@ -2373,10 +2370,10 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>102</v>
+        <v>8</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>122</v>
@@ -2387,16 +2384,30 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
